--- a/pensum/ma07/MA07_Pris_Oppgaver_v6.xlsx
+++ b/pensum/ma07/MA07_Pris_Oppgaver_v6.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="176">
   <si>
     <t xml:space="preserve">Pris som konkurransevirkemiddel: oppgaver til kapittel 7</t>
   </si>
@@ -165,15 +165,36 @@
     <t xml:space="preserve">Gule celler fyller du inn. Grønne regnes ut av arket. Sjekken til høyre forteller om svaret stemmer, og hva du bør se på hvis ikke.</t>
   </si>
   <si>
+    <t xml:space="preserve">Geografi</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 1B: Ti prisvirkemidler, fem situasjoner og bokas oppgave a</t>
   </si>
   <si>
+    <t xml:space="preserve">Kjøpstidspunkt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ulike mengder</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kari går gjennom alt Nordlys gjør med prisen, og spør for hvert virkemiddel: er dette prisdifferensiering etter boka, eller bare en lavere pris? Så ser hun på fem situasjoner og spør hvilken prissettingsmetode som veier tyngst. Til slutt regner hun bokas egen oppgave a.</t>
   </si>
   <si>
+    <t xml:space="preserve">Betalingstidspunkt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kunden gjør noe selv</t>
+  </si>
+  <si>
     <t xml:space="preserve">Prisdifferensiering er ulik pris fra ulike kjøpere for det samme produktet, og krever at minst ett av bokas seks kriterier er innfridd: geografisk atskilte markeder, ulikt kjøpstidspunkt, ulik alder, ulike mengder, ulikt betalingstidspunkt, eller at kunden gjør en oppgave selv. De tre rabattformene er kvantumsrabatt (mengder), kontantrabatt (betalingstidspunkt) og funksjonsrabatt (kunden gjør noe selv). Prissettingsmetodene er kostnadsbasert, konkurransebasert og etterspørselsbasert.</t>
   </si>
   <si>
+    <t xml:space="preserve">Ikke prisdifferensiering</t>
+  </si>
+  <si>
     <t xml:space="preserve">Testen</t>
   </si>
   <si>
@@ -273,7 +294,25 @@
     <t xml:space="preserve">e) Med egne ord: hvorfor er 10 % til en gammel kunde som truer med å bytte, ikke prisdifferensiering? Og hva skjer med prisen neste gang? (To–tre setninger. Bruk ordet kriterium.)</t>
   </si>
   <si>
+    <t xml:space="preserve">Kostnadsbasert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konkurransebasert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Etterspørselsbasert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rabatten tas av fortjenesten, ikke av prisen, så volumet må opp 61 %</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 1C: «Ti prosent, så signerer jeg i dag.» Hva svarer Kari?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Han har glemt merverdiavgiften</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingenting, ti prosent flere skap holder</t>
   </si>
   <si>
     <t xml:space="preserve">Styrelederen i borettslaget ringer Kari: ti prosent rabatt på sikringsskapbyttet, så signerer han i dag. Borettslaget har flere leiligheter som skal gjøres de neste tre årene. Ida har regnet 12 % fortjeneste på jobb 2614, og formann Ronny Fjeld sier at ti prosent rabatt bare betyr at de må selge ti prosent flere skap. Kari vil ha regnestykket før hun svarer.</t>
@@ -710,7 +749,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -805,6 +844,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1645,7 +1688,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G53"/>
+  <dimension ref="B1:Z85"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1653,17 +1696,26 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>45</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="24" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="6" t="s">
@@ -1674,6 +1726,9 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
+      <c r="Z3" s="24" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="7" t="s">
@@ -1684,16 +1739,22 @@
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
+      <c r="Z4" s="24" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="8" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
+      <c r="Z5" s="24" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="7" t="s">
@@ -1704,278 +1765,390 @@
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
+      <c r="Z6" s="24" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="8" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
+      <c r="Z7" s="24" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z8" s="0" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="7" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
+      <c r="Z9" s="24" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="8" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
+      <c r="Z10" s="24" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z11" s="0" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
+      <c r="B12" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="Z12" s="24" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="14" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C13" s="22"/>
       <c r="G13" s="17" t="str">
         <f aca="false">IF(C13="","Velg i nedtrekksmenyen.",IF(C13="Kjøpstidspunkt","Riktig. Kunden kjøper når etterspørselen er større enn kapasiteten, og betaler for å slippe å vente.","Ikke riktig. Kunden kjøper når etterspørselen er større enn kapasiteten, og betaler for å slippe å vente."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z13" s="24" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="14" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C14" s="22"/>
       <c r="G14" s="17" t="str">
         <f aca="false">IF(C14="","Velg i nedtrekksmenyen.",IF(C14="Kjøpstidspunkt","Riktig. Prisen brukes til å fylle kapasiteten når det er stille. Boka: prisen regulerer etterspørselen.","Ikke riktig. Prisen brukes til å fylle kapasiteten når det er stille. Boka: prisen regulerer etterspørselen."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z14" s="24" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="14" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C15" s="22"/>
       <c r="G15" s="17" t="str">
         <f aca="false">IF(C15="","Velg i nedtrekksmenyen.",IF(C15="Ulike mengder","Riktig. Kunden kjøper store mengder. Det er kvantumsrabatt.","Ikke riktig. Kunden kjøper store mengder. Det er kvantumsrabatt."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z15" s="24" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="14" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C16" s="22"/>
       <c r="G16" s="17" t="str">
         <f aca="false">IF(C16="","Velg i nedtrekksmenyen.",IF(C16="Ulike mengder","Riktig. Flere enheter i én jobb gir lavere pris per enhet: kvantumsrabatt.","Ikke riktig. Flere enheter i én jobb gir lavere pris per enhet: kvantumsrabatt."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z16" s="24" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="14" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C17" s="22"/>
       <c r="G17" s="17" t="str">
         <f aca="false">IF(C17="","Velg i nedtrekksmenyen.",IF(C17="Betalingstidspunkt","Riktig. Kunden betaler raskere enn vanlige betingelser. Det er kontantrabatt.","Ikke riktig. Kunden betaler raskere enn vanlige betingelser. Det er kontantrabatt."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z17" s="24" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="14" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C18" s="22"/>
       <c r="G18" s="17" t="str">
         <f aca="false">IF(C18="","Velg i nedtrekksmenyen.",IF(C18="Kunden gjør noe selv","Riktig. Kunden gjør en oppgave Nordlys ellers måtte gjort. Det er funksjonsrabatt.","Ikke riktig. Kunden gjør en oppgave Nordlys ellers måtte gjort. Det er funksjonsrabatt."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z18" s="24" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="14" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C19" s="22"/>
       <c r="G19" s="17" t="str">
         <f aca="false">IF(C19="","Velg i nedtrekksmenyen.",IF(C19="Kunden gjør noe selv","Riktig. Kunden yter noe i kjøpet som sparer montøren tid: funksjonsrabatt.","Ikke riktig. Kunden yter noe i kjøpet som sparer montøren tid: funksjonsrabatt."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z19" s="24" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="14" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C20" s="22"/>
       <c r="G20" s="17" t="str">
         <f aca="false">IF(C20="","Velg i nedtrekksmenyen.",IF(C20="Geografi","Riktig. Kundene er i geografisk atskilte markeder, og prisen følger stedet.","Ikke riktig. Kundene er i geografisk atskilte markeder, og prisen følger stedet."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z20" s="24" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="14" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C21" s="22"/>
       <c r="G21" s="17" t="str">
         <f aca="false">IF(C21="","Velg i nedtrekksmenyen.",IF(C21="Alder","Riktig. Kundene har ulik alder. Boka: honnørbillett, lavere kjøpekraft og bedre kapasitetsutnyttelse.","Ikke riktig. Kundene har ulik alder. Boka: honnørbillett, lavere kjøpekraft og bedre kapasitetsutnyttelse."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z21" s="24" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="14" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C22" s="22"/>
       <c r="G22" s="17" t="str">
         <f aca="false">IF(C22="","Velg i nedtrekksmenyen.",IF(C22="Ikke prisdifferensiering","Riktig. Kunden gjør ingenting annerledes. Ingen av de seks kriteriene er innfridd; det er bare en lavere pris, og den blir utgangspunktet neste gang.","Ikke riktig. Kunden gjør ingenting annerledes. Ingen av de seks kriteriene er innfridd; det er bare en lavere pris, og den blir utgangspunktet neste gang."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z22" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z23" s="0" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="24"/>
+      <c r="B24" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="Z24" s="24" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="14" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C25" s="22"/>
       <c r="G25" s="17" t="str">
         <f aca="false">IF(C25="","Velg i nedtrekksmenyen.",IF(C25="Konkurransebasert","Riktig. Kunden sammenligner, så konkurrentenes priser bestemmer. Selvkosten er likevel gulvet.","Ikke riktig. Kunden sammenligner, så konkurrentenes priser bestemmer. Selvkosten er likevel gulvet."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z25" s="24" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="14" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C26" s="22"/>
       <c r="G26" s="17" t="str">
         <f aca="false">IF(C26="","Velg i nedtrekksmenyen.",IF(C26="Etterspørselsbasert","Riktig. Kunden betaler for å slippe å vente. Prisen settes etter betalingsviljen, løsrevet fra egne kostnader.","Ikke riktig. Kunden betaler for å slippe å vente. Prisen settes etter betalingsviljen, løsrevet fra egne kostnader."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z26" s="24" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="14" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C27" s="22"/>
       <c r="G27" s="17" t="str">
         <f aca="false">IF(C27="","Velg i nedtrekksmenyen.",IF(C27="Kostnadsbasert","Riktig. Prisen bygges fra egne kalkyler: selvkost pluss fortjeneste. Selvkostmetoden.","Ikke riktig. Prisen bygges fra egne kalkyler: selvkost pluss fortjeneste. Selvkostmetoden."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z27" s="24" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="14" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C28" s="22"/>
       <c r="G28" s="17" t="str">
         <f aca="false">IF(C28="","Velg i nedtrekksmenyen.",IF(C28="Konkurransebasert","Riktig. Mange tilbyr nesten det samme, så prisen er gitt utenfra. Nordlys blir mengdetilpasser.","Ikke riktig. Mange tilbyr nesten det samme, så prisen er gitt utenfra. Nordlys blir mengdetilpasser."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z28" s="24" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="14" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C29" s="22"/>
       <c r="G29" s="17" t="str">
         <f aca="false">IF(C29="","Velg i nedtrekksmenyen.",IF(C29="Kostnadsbasert","Riktig. Prisen bygges opp fra kostnadene med påslag. Kostnadsbasert etter selvkostmetoden.","Ikke riktig. Prisen bygges opp fra kostnadene med påslag. Kostnadsbasert etter selvkostmetoden."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z29" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z30" s="0" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="7" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
       <c r="G31" s="7"/>
+      <c r="Z31" s="24" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="8" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8"/>
+      <c r="Z32" s="24" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="9" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>70</v>
+        <v>77</v>
+      </c>
+      <c r="Z33" s="24" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="11" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C34" s="12" t="n">
         <v>250</v>
       </c>
+      <c r="Z34" s="24" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="11" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C35" s="12" t="n">
         <v>10</v>
       </c>
+      <c r="Z35" s="24" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="11" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C36" s="12" t="n">
         <v>40</v>
       </c>
+      <c r="Z36" s="24" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="11" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C37" s="12" t="n">
         <v>10</v>
       </c>
+      <c r="Z37" s="24" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="11" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C38" s="12" t="n">
         <v>25</v>
       </c>
+      <c r="Z38" s="24" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z39" s="0" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C40" s="15"/>
       <c r="D40" s="16" t="s">
@@ -1985,10 +2158,13 @@
         <f aca="false">IF(C40="","Skriv svaret i den gule cellen.",IF(ABS(C40-(250+10))&lt;=0.01,"Riktig.",IF(ABS(C40-(250))&lt;=0.01,"Frakt og forsikring hører med i inntakskosten. Legg til 10 kr.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
+      <c r="Z40" s="24" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="14" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C41" s="15"/>
       <c r="D41" s="16" t="s">
@@ -1998,10 +2174,13 @@
         <f aca="false">IF(C41="","Skriv svaret i den gule cellen.",IF(ABS(C41-(260*1.4))&lt;=0.01,"Riktig.",IF(ABS(C41-(250*1.4))&lt;=0.01,"Du har regnet 40 % av innkjøpsprisen alene. Grunnlaget er inntakskosten, 260.",IF(ABS(C41-(260+40))&lt;=0.01,"40 er prosenten, ikke kronene. 40 % av 260 er 104.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
+      <c r="Z41" s="24" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="14" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C42" s="15"/>
       <c r="D42" s="16" t="s">
@@ -2011,10 +2190,13 @@
         <f aca="false">IF(C42="","Skriv svaret i den gule cellen.",IF(ABS(C42-(260*1.4*1.1))&lt;=0.01,"Riktig.",IF(ABS(C42-(260*1.4+26))&lt;=0.01,"Du har regnet 10 % av 260. Fortjenesten regnes av selvkosten, 364.",IF(ABS(C42-(260*1.5))&lt;=0.01,"Du har lagt 40 % og 10 % sammen til 50 %. Fortjenesten regnes av selvkosten, etter at de indirekte er lagt på: 364 × 1,10.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
+      <c r="Z42" s="24" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="14" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C43" s="15"/>
       <c r="D43" s="16" t="s">
@@ -2024,16 +2206,27 @@
         <f aca="false">IF(C43="","Skriv svaret i den gule cellen.",IF(ABS(C43-(260*1.4*1.1*1.25))&lt;=0.01,"Riktig.",IF(ABS(C43-(260*1.4*1.25))&lt;=0.01,"Du har glemt fortjenesten. Først 10 % på selvkost, så merverdiavgift.",IF(ABS(C43-(260*1.4*1.1+25))&lt;=0.01,"25 er prosenten, ikke kronene. 25 % av 400,40 er 100,10.",IF(ABS(C43-(260*1.4*1.1*0.25))&lt;=0.01,"Det er bare avgiften. Utsalgsprisen er prisen uten avgift pluss avgiften: gang med 1,25.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
+      <c r="Z43" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z44" s="0" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="8" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
       <c r="G45" s="8"/>
+      <c r="Z45" s="24" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="19"/>
@@ -2042,6 +2235,9 @@
       <c r="E46" s="19"/>
       <c r="F46" s="19"/>
       <c r="G46" s="19"/>
+      <c r="Z46" s="24" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="19"/>
@@ -2050,6 +2246,9 @@
       <c r="E47" s="19"/>
       <c r="F47" s="19"/>
       <c r="G47" s="19"/>
+      <c r="Z47" s="24" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="19"/>
@@ -2058,6 +2257,9 @@
       <c r="E48" s="19"/>
       <c r="F48" s="19"/>
       <c r="G48" s="19"/>
+      <c r="Z48" s="24" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="20" t="str">
@@ -2069,12 +2271,18 @@
       <c r="E49" s="20"/>
       <c r="F49" s="20"/>
       <c r="G49" s="20"/>
+      <c r="Z49" s="24" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="21" t="s">
         <v>43</v>
       </c>
       <c r="C50" s="22"/>
+      <c r="Z50" s="24" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="23" t="str">
@@ -2086,6 +2294,14 @@
       <c r="E51" s="23"/>
       <c r="F51" s="23"/>
       <c r="G51" s="23"/>
+      <c r="Z51" s="24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z52" s="0" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="6" t="s">
@@ -2096,6 +2312,169 @@
       <c r="E53" s="6"/>
       <c r="F53" s="6"/>
       <c r="G53" s="6"/>
+      <c r="Z53" s="24" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z54" s="0" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z55" s="0" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z56" s="0" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z57" s="0" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z58" s="0" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z59" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z60" s="0" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z61" s="0" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z62" s="0" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z63" s="0" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z64" s="0" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z65" s="0" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z66" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z67" s="0" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z68" s="0" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z69" s="0" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z70" s="0" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z71" s="0" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z72" s="0" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z73" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z74" s="0" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z75" s="0" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z76" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z77" s="0" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z78" s="0" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z79" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z80" s="0" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z81" s="0" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z82" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z83" s="0" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z84" s="0" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z85" s="0" t="s">
+        <v>90</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -2271,63 +2650,63 @@
   </conditionalFormatting>
   <dataValidations count="16">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C13" type="list">
-      <formula1>"Geografi,Kjøpstidspunkt,Alder,Ulike mengder,Betalingstidspunkt,Kunden gjør noe selv,Ikke prisdifferensiering"</formula1>
+      <formula1>$Z$1:$Z$7</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C14" type="list">
-      <formula1>"Geografi,Kjøpstidspunkt,Alder,Ulike mengder,Betalingstidspunkt,Kunden gjør noe selv,Ikke prisdifferensiering"</formula1>
+      <formula1>$Z$8:$Z$14</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C15" type="list">
-      <formula1>"Geografi,Kjøpstidspunkt,Alder,Ulike mengder,Betalingstidspunkt,Kunden gjør noe selv,Ikke prisdifferensiering"</formula1>
+      <formula1>$Z$15:$Z$21</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C16" type="list">
-      <formula1>"Geografi,Kjøpstidspunkt,Alder,Ulike mengder,Betalingstidspunkt,Kunden gjør noe selv,Ikke prisdifferensiering"</formula1>
+      <formula1>$Z$22:$Z$28</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C17" type="list">
-      <formula1>"Geografi,Kjøpstidspunkt,Alder,Ulike mengder,Betalingstidspunkt,Kunden gjør noe selv,Ikke prisdifferensiering"</formula1>
+      <formula1>$Z$29:$Z$35</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C18" type="list">
-      <formula1>"Geografi,Kjøpstidspunkt,Alder,Ulike mengder,Betalingstidspunkt,Kunden gjør noe selv,Ikke prisdifferensiering"</formula1>
+      <formula1>$Z$36:$Z$42</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C19" type="list">
-      <formula1>"Geografi,Kjøpstidspunkt,Alder,Ulike mengder,Betalingstidspunkt,Kunden gjør noe selv,Ikke prisdifferensiering"</formula1>
+      <formula1>$Z$43:$Z$49</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C20" type="list">
-      <formula1>"Geografi,Kjøpstidspunkt,Alder,Ulike mengder,Betalingstidspunkt,Kunden gjør noe selv,Ikke prisdifferensiering"</formula1>
+      <formula1>$Z$50:$Z$56</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C21" type="list">
-      <formula1>"Geografi,Kjøpstidspunkt,Alder,Ulike mengder,Betalingstidspunkt,Kunden gjør noe selv,Ikke prisdifferensiering"</formula1>
+      <formula1>$Z$57:$Z$63</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C22" type="list">
-      <formula1>"Geografi,Kjøpstidspunkt,Alder,Ulike mengder,Betalingstidspunkt,Kunden gjør noe selv,Ikke prisdifferensiering"</formula1>
+      <formula1>$Z$64:$Z$70</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C25" type="list">
-      <formula1>"Kostnadsbasert,Konkurransebasert,Etterspørselsbasert"</formula1>
+      <formula1>$Z$71:$Z$73</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C26" type="list">
-      <formula1>"Kostnadsbasert,Konkurransebasert,Etterspørselsbasert"</formula1>
+      <formula1>$Z$74:$Z$76</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C27" type="list">
-      <formula1>"Kostnadsbasert,Konkurransebasert,Etterspørselsbasert"</formula1>
+      <formula1>$Z$77:$Z$79</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C28" type="list">
-      <formula1>"Kostnadsbasert,Konkurransebasert,Etterspørselsbasert"</formula1>
+      <formula1>$Z$80:$Z$82</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C29" type="list">
-      <formula1>"Kostnadsbasert,Konkurransebasert,Etterspørselsbasert"</formula1>
+      <formula1>$Z$83:$Z$85</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C50" type="list">
@@ -2350,7 +2729,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G42"/>
+  <dimension ref="B1:Z42"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -2358,17 +2737,26 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>91</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="24" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="6" t="s">
@@ -2379,6 +2767,9 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
+      <c r="Z3" s="24" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="7" t="s">
@@ -2392,7 +2783,7 @@
     </row>
     <row r="5" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="8" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -2412,7 +2803,7 @@
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="8" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -2432,7 +2823,7 @@
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="8" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -2442,7 +2833,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="9" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>22</v>
@@ -2450,59 +2841,59 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="C12" s="25" t="n">
+        <v>99</v>
+      </c>
+      <c r="C12" s="26" t="n">
         <v>26611.2</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="C13" s="25" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" s="26" t="n">
         <v>19560</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="C14" s="25" t="n">
+        <v>101</v>
+      </c>
+      <c r="C14" s="26" t="n">
         <v>23760</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" s="26" t="n">
+        <v>102</v>
+      </c>
+      <c r="C15" s="27" t="n">
         <f aca="false">C12-C14</f>
         <v>2851.2</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" s="26" t="n">
+        <v>103</v>
+      </c>
+      <c r="C16" s="27" t="n">
         <f aca="false">C12-C13</f>
         <v>7051.2</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="C17" s="25" t="n">
+        <v>104</v>
+      </c>
+      <c r="C17" s="26" t="n">
         <v>890</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="C18" s="25" t="n">
+        <v>105</v>
+      </c>
+      <c r="C18" s="26" t="n">
         <v>796.67</v>
       </c>
     </row>
@@ -2518,7 +2909,7 @@
     </row>
     <row r="21" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="8" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
@@ -2528,7 +2919,7 @@
     </row>
     <row r="23" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="14" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="16" t="s">
@@ -2541,7 +2932,7 @@
     </row>
     <row r="24" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="14" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="C24" s="15"/>
       <c r="D24" s="16" t="s">
@@ -2554,7 +2945,7 @@
     </row>
     <row r="25" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="14" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="C25" s="15"/>
       <c r="D25" s="16" t="s">
@@ -2567,11 +2958,11 @@
     </row>
     <row r="26" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="C26" s="27"/>
+        <v>110</v>
+      </c>
+      <c r="C26" s="28"/>
       <c r="D26" s="16" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="G26" s="17" t="str">
         <f aca="false">IF(C26="","Skriv svaret i den gule cellen.",IF(ABS(C26-(ROUND(26611.2*0.1/(26611.2-23760)*100,0)))&lt;=0.5,"Riktig.",IF(ABS(C26-(10))&lt;=0.5,"Rabatten er 10 % av prisen, men fortjenesten er bare en liten del av prisen. Regn rabatten i kroner delt på fortjenesten ved full pris.",IF(ABS(C26-(ROUND(26611.2*0.1/(26611.2-19560)*100,0)))&lt;=0.5,"Du har delt på dekningsbidraget. Oppgaven spør om fortjenesten over selvkost, 2 851,20.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
@@ -2580,7 +2971,7 @@
     </row>
     <row r="27" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="14" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="C27" s="15"/>
       <c r="D27" s="16" t="s">
@@ -2593,7 +2984,7 @@
     </row>
     <row r="28" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="14" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="C28" s="15"/>
       <c r="D28" s="16" t="s">
@@ -2606,11 +2997,11 @@
     </row>
     <row r="29" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="C29" s="27"/>
+        <v>114</v>
+      </c>
+      <c r="C29" s="28"/>
       <c r="D29" s="16" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="G29" s="17" t="str">
         <f aca="false">IF(C29="","Skriv svaret i den gule cellen.",IF(ABS(C29-(ROUND(((26611.2-19560)/(26611.2*0.9-19560)-1)*100,0)))&lt;=0.5,"Riktig.",IF(ABS(C29-(10))&lt;=0.5,"Det er Ronnys svar, og det stemmer ikke. Det er dekningsbidraget som skal tas igjen, ikke prisen. Del gammelt dekningsbidrag på nytt.",IF(ABS(C29-(ROUND((26611.2*0.9-19560)/(26611.2-19560)*100,0)))&lt;=0.5,"Du har delt nytt dekningsbidrag på gammelt. Snu brøken: gammelt delt på nytt, og trekk fra 1.","Ikke riktig ennå. Gammelt dekningsbidrag 7 051,20 delt på nytt 4 390,08 gir 1,61. Det er 61 % flere skap."))))</f>
@@ -2619,11 +3010,11 @@
     </row>
     <row r="30" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="14" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="C30" s="15"/>
       <c r="D30" s="16" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="G30" s="17" t="str">
         <f aca="false">IF(C30="","Skriv svaret i den gule cellen.",IF(ABS(C30-(890*0.9-796.67))&lt;=0.01,"Riktig.",IF(ABS(C30-((890-796.67)*0.9))&lt;=0.01,"Du har trukket 10 % av fortjenesten per time. Rabatten er 10 % av 890, altså 89 kr, og hele beløpet går av fortjenesten.",IF(ABS(C30-(890*0.1))&lt;=0.01,"Det er rabatten, 89 kr. Spørsmålet er hva som er igjen: 801 minus 796,67.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
@@ -2632,7 +3023,7 @@
     </row>
     <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="14" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="C32" s="22"/>
       <c r="G32" s="17" t="str">
@@ -2642,7 +3033,7 @@
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="8" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
@@ -2804,7 +3195,7 @@
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C32" type="list">
-      <formula1>"Rabatten tas av fortjenesten,ikke av prisen,så volumet må opp 61 %,Han har glemt merverdiavgiften,Ingenting,ti prosent flere skap holder"</formula1>
+      <formula1>$Z$1:$Z$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C39" type="list">
@@ -2837,300 +3228,300 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="28" t="s">
-        <v>106</v>
+      <c r="B2" s="29" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="6" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="29" t="s">
-        <v>108</v>
-      </c>
-      <c r="C5" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="D5" s="29" t="s">
-        <v>110</v>
+      <c r="B5" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="30" t="s">
-        <v>111</v>
+      <c r="B6" s="31" t="s">
+        <v>124</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>26611.2</v>
       </c>
-      <c r="D6" s="30" t="s">
-        <v>112</v>
+      <c r="D6" s="31" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="30" t="s">
-        <v>113</v>
+      <c r="B7" s="31" t="s">
+        <v>126</v>
       </c>
       <c r="C7" s="13" t="n">
         <v>33264</v>
       </c>
-      <c r="D7" s="30" t="s">
-        <v>114</v>
+      <c r="D7" s="31" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="30" t="s">
-        <v>115</v>
+      <c r="B8" s="31" t="s">
+        <v>128</v>
       </c>
       <c r="C8" s="13" t="n">
         <v>24400</v>
       </c>
-      <c r="D8" s="30" t="s">
-        <v>116</v>
+      <c r="D8" s="31" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="30" t="s">
-        <v>117</v>
+      <c r="B9" s="31" t="s">
+        <v>130</v>
       </c>
       <c r="C9" s="13" t="n">
         <v>28720</v>
       </c>
-      <c r="D9" s="30" t="s">
-        <v>118</v>
+      <c r="D9" s="31" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="30" t="s">
-        <v>119</v>
+      <c r="B10" s="31" t="s">
+        <v>132</v>
       </c>
       <c r="C10" s="13" t="n">
         <v>2851.2</v>
       </c>
-      <c r="D10" s="30" t="s">
-        <v>120</v>
+      <c r="D10" s="31" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="30" t="s">
-        <v>121</v>
+      <c r="B11" s="31" t="s">
+        <v>134</v>
       </c>
       <c r="C11" s="13" t="n">
         <v>640</v>
       </c>
-      <c r="D11" s="30" t="s">
-        <v>122</v>
+      <c r="D11" s="31" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="30" t="s">
-        <v>123</v>
+      <c r="B12" s="31" t="s">
+        <v>136</v>
       </c>
       <c r="C12" s="13" t="n">
         <v>4960</v>
       </c>
-      <c r="D12" s="30" t="s">
-        <v>124</v>
+      <c r="D12" s="31" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="30" t="s">
-        <v>125</v>
+      <c r="B13" s="31" t="s">
+        <v>138</v>
       </c>
       <c r="C13" s="13" t="n">
         <v>20.9</v>
       </c>
-      <c r="D13" s="30" t="s">
-        <v>126</v>
+      <c r="D13" s="31" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="30" t="s">
-        <v>127</v>
+      <c r="B14" s="31" t="s">
+        <v>140</v>
       </c>
       <c r="C14" s="13"/>
-      <c r="D14" s="30" t="s">
-        <v>128</v>
+      <c r="D14" s="31" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="30" t="s">
-        <v>129</v>
+      <c r="B15" s="31" t="s">
+        <v>142</v>
       </c>
       <c r="C15" s="13"/>
-      <c r="D15" s="30" t="s">
-        <v>130</v>
+      <c r="D15" s="31" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="30" t="s">
-        <v>131</v>
+      <c r="B16" s="31" t="s">
+        <v>144</v>
       </c>
       <c r="C16" s="13"/>
-      <c r="D16" s="30" t="s">
-        <v>132</v>
+      <c r="D16" s="31" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="30" t="s">
-        <v>133</v>
+      <c r="B17" s="31" t="s">
+        <v>146</v>
       </c>
       <c r="C17" s="13" t="n">
         <v>260</v>
       </c>
-      <c r="D17" s="30" t="s">
-        <v>134</v>
+      <c r="D17" s="31" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="30" t="s">
-        <v>135</v>
+      <c r="B18" s="31" t="s">
+        <v>148</v>
       </c>
       <c r="C18" s="13" t="n">
         <v>364</v>
       </c>
-      <c r="D18" s="30" t="s">
-        <v>136</v>
+      <c r="D18" s="31" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="30" t="s">
-        <v>137</v>
+      <c r="B19" s="31" t="s">
+        <v>150</v>
       </c>
       <c r="C19" s="13" t="n">
         <v>400.4</v>
       </c>
-      <c r="D19" s="30" t="s">
-        <v>138</v>
+      <c r="D19" s="31" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="30" t="s">
-        <v>139</v>
+      <c r="B20" s="31" t="s">
+        <v>152</v>
       </c>
       <c r="C20" s="13" t="n">
         <v>500.5</v>
       </c>
-      <c r="D20" s="30" t="s">
-        <v>140</v>
+      <c r="D20" s="31" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="30" t="s">
-        <v>141</v>
+      <c r="B21" s="31" t="s">
+        <v>154</v>
       </c>
       <c r="C21" s="13"/>
-      <c r="D21" s="30" t="s">
-        <v>142</v>
+      <c r="D21" s="31" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="30" t="s">
-        <v>143</v>
+      <c r="B22" s="31" t="s">
+        <v>156</v>
       </c>
       <c r="C22" s="13" t="n">
         <v>23950.08</v>
       </c>
-      <c r="D22" s="30" t="s">
-        <v>144</v>
+      <c r="D22" s="31" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="30" t="s">
-        <v>145</v>
+      <c r="B23" s="31" t="s">
+        <v>158</v>
       </c>
       <c r="C23" s="13" t="n">
         <v>190.08</v>
       </c>
-      <c r="D23" s="30" t="s">
-        <v>146</v>
+      <c r="D23" s="31" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="30" t="s">
-        <v>147</v>
+      <c r="B24" s="31" t="s">
+        <v>160</v>
       </c>
       <c r="C24" s="13" t="n">
         <v>4390.08</v>
       </c>
-      <c r="D24" s="30" t="s">
-        <v>148</v>
+      <c r="D24" s="31" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="30" t="s">
-        <v>149</v>
+      <c r="B25" s="31" t="s">
+        <v>162</v>
       </c>
       <c r="C25" s="13" t="n">
         <v>93</v>
       </c>
-      <c r="D25" s="30" t="s">
-        <v>150</v>
+      <c r="D25" s="31" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="30" t="s">
-        <v>151</v>
+      <c r="B26" s="31" t="s">
+        <v>164</v>
       </c>
       <c r="C26" s="13" t="n">
         <v>25280.64</v>
       </c>
-      <c r="D26" s="30" t="s">
-        <v>152</v>
+      <c r="D26" s="31" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="30" t="s">
-        <v>153</v>
+      <c r="B27" s="31" t="s">
+        <v>166</v>
       </c>
       <c r="C27" s="13" t="n">
         <v>1520.64</v>
       </c>
-      <c r="D27" s="30" t="s">
-        <v>154</v>
+      <c r="D27" s="31" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="30" t="s">
-        <v>155</v>
+      <c r="B28" s="31" t="s">
+        <v>168</v>
       </c>
       <c r="C28" s="13" t="n">
         <v>61</v>
       </c>
-      <c r="D28" s="30" t="s">
-        <v>156</v>
+      <c r="D28" s="31" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="30" t="s">
-        <v>157</v>
+      <c r="B29" s="31" t="s">
+        <v>170</v>
       </c>
       <c r="C29" s="13" t="n">
         <v>4.33</v>
       </c>
-      <c r="D29" s="30" t="s">
-        <v>158</v>
+      <c r="D29" s="31" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="30" t="s">
-        <v>159</v>
+      <c r="B30" s="31" t="s">
+        <v>172</v>
       </c>
       <c r="C30" s="13"/>
-      <c r="D30" s="30" t="s">
-        <v>160</v>
+      <c r="D30" s="31" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="30" t="s">
-        <v>161</v>
+      <c r="B31" s="31" t="s">
+        <v>174</v>
       </c>
       <c r="C31" s="13"/>
-      <c r="D31" s="30" t="s">
-        <v>162</v>
+      <c r="D31" s="31" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/pensum/ma07/MA07_Pris_Oppgaver_v6.xlsx
+++ b/pensum/ma07/MA07_Pris_Oppgaver_v6.xlsx
@@ -207,7 +207,7 @@
     <t xml:space="preserve">Hastetillegg 30 % på oppdrag samme dag</t>
   </si>
   <si>
-    <t xml:space="preserve">Lavere pris på el-sjekk i en stille januar</t>
+    <t xml:space="preserve">Lavere pris på el-sjekk i en stille uke i august, rett etter fellesferien</t>
   </si>
   <si>
     <t xml:space="preserve">Rammeavtale med et borettslag om alle leilighetene, 10 % under timeprisen</t>
@@ -219,7 +219,7 @@
     <t xml:space="preserve">2 % avslag når fakturaen betales innen 8 dager</t>
   </si>
   <si>
-    <t xml:space="preserve">Kunden henter materiellet hos Polarlys selv</t>
+    <t xml:space="preserve">Kunden bærer ut det gamle skapet og leverer det til gjenvinning selv</t>
   </si>
   <si>
     <t xml:space="preserve">Kunden rydder tilkomsten til sikringsskapet selv</t>
@@ -243,10 +243,10 @@
     <t xml:space="preserve">Butikken uten strøm i kjøledisken fredag klokka 15</t>
   </si>
   <si>
-    <t xml:space="preserve">Nordlys' timepris 890 kr, regnet fra selvkost 796,67 kr per fakturert time pluss fortjeneste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ren utleie av montørtimer til et annet firma, til den prisen markedet gir</t>
+    <t xml:space="preserve">Ida priser et stort anbud som selvkost pluss 12 % fortjeneste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ida legger et standard boligtilbud på samme nivå som de fem konkurrentene i bydelen</t>
   </si>
   <si>
     <t xml:space="preserve">Bokas oppgave a: innkjøp 250 kr pluss påslag for indirekte kostnader, fortjeneste og merverdiavgift</t>
@@ -303,7 +303,7 @@
     <t xml:space="preserve">Etterspørselsbasert</t>
   </si>
   <si>
-    <t xml:space="preserve">Rabatten tas av fortjenesten, ikke av prisen, så volumet må opp 61 %</t>
+    <t xml:space="preserve">Rabatten tas av dekningsbidraget, ikke av prisen, så volumet må opp 61 %</t>
   </si>
   <si>
     <t xml:space="preserve">Oppgave 1C: «Ti prosent, så signerer jeg i dag.» Hva svarer Kari?</t>
@@ -345,14 +345,14 @@
     <t xml:space="preserve">Timepris per montørtime, uten merverdiavgift</t>
   </si>
   <si>
-    <t xml:space="preserve">Selvkost per fakturert time (11 472 000 / 14 400)</t>
+    <t xml:space="preserve">Selvkost per fakturert time (faktaarket)</t>
   </si>
   <si>
     <t xml:space="preserve">1. Styrelederen vil ha 10 % rabatt. Regn ny pris (prisen ganger 0,90), fortjenesten over selvkost og dekningsbidraget ved den nye prisen. Selvkosten og de variable kostnadene står stille.
 2. Regn hvor mange prosent av fortjenesten som forsvinner.
 3. Gjør det samme med 5 % rabatt: ny pris og fortjeneste.
 4. Volumkravet: gammelt dekningsbidrag delt på nytt sier hvor mange skap Nordlys må selge for hvert skap før. Svar i prosent flere skap, hele prosent.
-5. Timeprisen: hva er igjen per time når 890 kr settes ned 10 % og selvkosten er 796,67?
+5. Timeprisen: hva er igjen per time over selvkosten når 890 kr settes ned 10 % og selvkosten er 907? Svaret blir negativt.
 6. Velg i i hva som er feil i Ronnys resonnement, og skriv Karis motbud i j. Svar med to desimaler der det trengs.</t>
   </si>
   <si>
@@ -380,7 +380,7 @@
     <t xml:space="preserve">g) Volumkravet ved 10 % rabatt: hvor mange prosent flere skap må Nordlys selge for samme dekningsbidrag? (hele prosent)</t>
   </si>
   <si>
-    <t xml:space="preserve">h) Timeprisen 890 kr med 10 % rabatt: hva er igjen per time over selvkosten 796,67?</t>
+    <t xml:space="preserve">h) Timeprisen 890 kr med 10 % rabatt: hva er igjen per time over selvkosten 907? (negativt tall)</t>
   </si>
   <si>
     <t xml:space="preserve">kr per time</t>
@@ -464,13 +464,13 @@
     <t xml:space="preserve">1B Kriteriene</t>
   </si>
   <si>
-    <t xml:space="preserve">Kjøpstidspunkt: hastetillegg, januar. Ulike mengder: rammeavtalen, tolv ladepunkter. Betalingstidspunkt: 2 % innen 8 dager. Kunden gjør noe selv: henter materiellet, rydder tilkomsten. Geografi: kjøretillegg. Alder: honnørpris. Ikke prisdifferensiering: 10 % til den gamle kunden</t>
+    <t xml:space="preserve">Kjøpstidspunkt: hastetillegg, stille uke i august. Ulike mengder: rammeavtalen, tolv ladepunkter. Betalingstidspunkt: 2 % innen 8 dager. Kunden gjør noe selv: bærer ut skapet, rydder tilkomsten. Geografi: kjøretillegg. Alder: honnørpris. Ikke prisdifferensiering: 10 % til den gamle kunden</t>
   </si>
   <si>
     <t xml:space="preserve">1B Metodene</t>
   </si>
   <si>
-    <t xml:space="preserve">Skapbytte med tre tilbud: konkurransebasert. Kjøledisken: etterspørselsbasert. Timeprisen fra selvkost: kostnadsbasert. Ren timeutleie: konkurransebasert. Bokas oppgave a: kostnadsbasert (selvkostmetoden)</t>
+    <t xml:space="preserve">Skapbytte med tre tilbud: konkurransebasert. Kjøledisken: etterspørselsbasert. Anbudet fra selvkost pluss 12 %: kostnadsbasert. Tilbudet på konkurrentenes nivå: konkurransebasert. Bokas oppgave a: kostnadsbasert (selvkostmetoden)</t>
   </si>
   <si>
     <t xml:space="preserve">1B a) Inntakskost</t>
@@ -548,13 +548,13 @@
     <t xml:space="preserve">1C h) Igjen per time</t>
   </si>
   <si>
-    <t xml:space="preserve">890 × 0,90 = 801. 801 − 796,67 = 4,33 kr</t>
+    <t xml:space="preserve">890 × 0,90 = 801. 801 − 907 = −106 kr. Allerede 890 ligger under selvkost (faktaarket); påslaget på materiellet bærer timene</t>
   </si>
   <si>
     <t xml:space="preserve">1C i) Ronnys feil</t>
   </si>
   <si>
-    <t xml:space="preserve">Rabatten tas av fortjenesten, ikke av prisen. Volumet må opp 61 %, ikke 10 %</t>
+    <t xml:space="preserve">Rabatten tas av dekningsbidraget (og dermed av fortjenesten), ikke av prisen. Volumet må opp 7 051,20 / 4 390,08 − 1 = 61 %, ikke 10 %</t>
   </si>
   <si>
     <t xml:space="preserve">1C j) Karis motbud</t>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="C28" s="22"/>
       <c r="G28" s="17" t="str">
-        <f aca="false">IF(C28="","Velg i nedtrekksmenyen.",IF(C28="Konkurransebasert","Riktig. Mange tilbyr nesten det samme, så prisen er gitt utenfra. Nordlys blir mengdetilpasser.","Ikke riktig. Mange tilbyr nesten det samme, så prisen er gitt utenfra. Nordlys blir mengdetilpasser."))</f>
+        <f aca="false">IF(C28="","Velg i nedtrekksmenyen.",IF(C28="Konkurransebasert","Riktig. Konkurrentenes priser setter rammen for prisen. Konkurransebasert prissetting.","Ikke riktig. Konkurrentenes priser setter rammen for prisen. Konkurransebasert prissetting."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
       <c r="Z28" s="24" t="s">
@@ -2894,7 +2894,7 @@
         <v>105</v>
       </c>
       <c r="C18" s="26" t="n">
-        <v>796.67</v>
+        <v>907</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3017,7 +3017,7 @@
         <v>116</v>
       </c>
       <c r="G30" s="17" t="str">
-        <f aca="false">IF(C30="","Skriv svaret i den gule cellen.",IF(ABS(C30-(890*0.9-796.67))&lt;=0.01,"Riktig.",IF(ABS(C30-((890-796.67)*0.9))&lt;=0.01,"Du har trukket 10 % av fortjenesten per time. Rabatten er 10 % av 890, altså 89 kr, og hele beløpet går av fortjenesten.",IF(ABS(C30-(890*0.1))&lt;=0.01,"Det er rabatten, 89 kr. Spørsmålet er hva som er igjen: 801 minus 796,67.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
+        <f aca="false">IF(C30="","Skriv svaret i den gule cellen.",IF(ABS(C30-(890*0.9-907))&lt;=0.01,"Riktig.",IF(ABS(C30-((890-907)*0.9))&lt;=0.01,"Du har tatt 10 % av differansen. Rabatten er 10 % av 890, altså 89 kr, og hele beløpet går av: 801 minus 907.",IF(ABS(C30-(890*0.1))&lt;=0.01,"Det er rabatten, 89 kr. Spørsmålet er hva som er igjen: 801 minus 907.",IF(ABS(C30-(907-890*0.9))&lt;=0.01,"Riktig størrelse, men feil fortegn. Prisen er lavere enn selvkosten, så svaret er negativt.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="C32" s="22"/>
       <c r="G32" s="17" t="str">
-        <f aca="false">IF(C32="","Velg i nedtrekksmenyen.",IF(C32="Rabatten tas av fortjenesten, ikke av prisen, så volumet må opp 61 %","Riktig. Kostnadene står stille, så hele rabatten går av dekningsbidraget. 7 051,20 / 4 390,08 = 1,61: Nordlys må selge 61 % flere skap, ikke 10 %.","Ikke riktig. Kostnadene står stille, så hele rabatten går av dekningsbidraget. 7 051,20 / 4 390,08 = 1,61: Nordlys må selge 61 % flere skap, ikke 10 %."))</f>
+        <f aca="false">IF(C32="","Velg i nedtrekksmenyen.",IF(C32="Rabatten tas av dekningsbidraget, ikke av prisen, så volumet må opp 61 %","Riktig. Kostnadene står stille, så hele rabatten går av dekningsbidraget. 7 051,20 / 4 390,08 = 1,61: Nordlys må selge 61 % flere skap, ikke 10 %.","Ikke riktig. Kostnadene står stille, så hele rabatten går av dekningsbidraget. 7 051,20 / 4 390,08 = 1,61: Nordlys må selge 61 % flere skap, ikke 10 %."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
@@ -3082,9 +3082,9 @@
       </c>
       <c r="C39" s="22"/>
     </row>
-    <row r="40" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="23" t="str">
-        <f aca="false">IF(C39="JA","Hint: a: 26 611,20 × 0,90 = 23 950,08. b: 23 950,08 − 23 760 = 190,08. c: 23 950,08 − 19 560 = 4 390,08. d: 2 661,12 / 2 851,20 = 93 %. e: 26 611,20 × 0,95 = 25 280,64. f: 25 280,64 − 23 760 = 1 520,64. g: 7 051,20 / 4 390,08 = 1,61, altså 61 % flere. h: 801 − 796,67 = 4,33.","")</f>
+        <f aca="false">IF(C39="JA","Hint: a: 26 611,20 × 0,90 = 23 950,08. b: 23 950,08 − 23 760 = 190,08. c: 23 950,08 − 19 560 = 4 390,08. d: 2 661,12 / 2 851,20 = 93 %. e: 26 611,20 × 0,95 = 25 280,64. f: 25 280,64 − 23 760 = 1 520,64. g: 7 051,20 / 4 390,08 = 1,61, altså 61 % flere. h: 801 − 907 = −106: timen med rabatt dekker ikke selvkost, og påslaget på materiellet må bære resten.","")</f>
         <v/>
       </c>
       <c r="C40" s="23"/>
@@ -3500,7 +3500,7 @@
         <v>170</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>4.33</v>
+        <v>-106</v>
       </c>
       <c r="D29" s="31" t="s">
         <v>171</v>

--- a/pensum/ma07/MA07_Pris_Oppgaver_v6.xlsx
+++ b/pensum/ma07/MA07_Pris_Oppgaver_v6.xlsx
@@ -749,7 +749,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -876,6 +876,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1163,7 +1167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -1188,27 +1192,27 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="2" t="s">
         <v>11</v>
       </c>
@@ -1332,8 +1336,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="s">
+    <row ht="31.5" customHeight="true" r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="32" r="B12" t="s">
         <v>23</v>
       </c>
       <c r="C12" s="12" t="n">
@@ -1818,7 +1822,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="25" t="s">
         <v>57</v>
       </c>
@@ -1966,7 +1970,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="24" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="25" t="s">
         <v>68</v>
       </c>
@@ -2872,8 +2876,8 @@
         <v>2851.2</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="11" t="s">
+    <row ht="31.5" customHeight="true" r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="32" r="B16" t="s">
         <v>103</v>
       </c>
       <c r="C16" s="27" t="n">
@@ -2907,7 +2911,7 @@
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
     </row>
-    <row r="21" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="105" customHeight="true" r="21" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="8" t="s">
         <v>106</v>
       </c>
@@ -2995,7 +2999,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="29" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="14" t="s">
         <v>114</v>
       </c>
